--- a/data/trans_orig/IP07A18-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A18-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que se riesen de él/ella otros chicos en 2007 (tasa de respuesta: 99,1%)</t>
+          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el adulto en 2007 (tasa de respuesta: 99,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>8019</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>12590</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9224</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>9398</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17580</t>
+          <t>17894</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39396</t>
+          <t>39447</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28020</t>
+          <t>27784</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38027</t>
+          <t>38448</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60666</t>
+          <t>59421</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>75045</t>
+          <t>74244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>75,83%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11292</t>
+          <t>11861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17841</t>
+          <t>17254</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16469</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12457</t>
+          <t>12297</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13036</t>
+          <t>12387</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>25571</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18194</t>
+          <t>18530</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32723</t>
+          <t>33366</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18706</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34779</t>
+          <t>33999</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41480</t>
+          <t>41618</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62158</t>
+          <t>62652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144396</t>
+          <t>144738</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163276</t>
+          <t>163280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>181628</t>
+          <t>181655</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>201892</t>
+          <t>200963</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>332697</t>
+          <t>331879</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>359079</t>
+          <t>359085</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>732</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12431</t>
+          <t>12208</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>744</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>488</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16879</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28079</t>
+          <t>28206</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42726</t>
+          <t>42913</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54432</t>
+          <t>54428</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37144</t>
+          <t>37296</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48622</t>
+          <t>49219</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83117</t>
+          <t>83475</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>99774</t>
+          <t>99816</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>13577</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19818</t>
+          <t>19351</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14909</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20131</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17715</t>
+          <t>18748</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>17852</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>34043</t>
+          <t>33968</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24095</t>
+          <t>23644</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>17779</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20602</t>
+          <t>20586</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>37252</t>
+          <t>38001</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34237</t>
+          <t>33604</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53543</t>
+          <t>52873</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31149</t>
+          <t>31399</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50721</t>
+          <t>49887</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70125</t>
+          <t>70336</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>96458</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>224753</t>
+          <t>225649</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>250263</t>
+          <t>250763</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>254304</t>
+          <t>256237</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>280096</t>
+          <t>279749</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>490736</t>
+          <t>487335</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>524086</t>
+          <t>523011</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,88%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que se riesen de él/ella otros chicos en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17785</t>
+          <t>17680</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>426</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>7832</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11674</t>
+          <t>11918</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10528</t>
+          <t>10353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10339</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>17220</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27685</t>
+          <t>27904</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40180</t>
+          <t>39230</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25886</t>
+          <t>25969</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36144</t>
+          <t>36010</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56772</t>
+          <t>56516</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72305</t>
+          <t>72189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,97%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>17235</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22407</t>
+          <t>23435</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,47 +4423,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>10,28%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>27081</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>19040</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>35344</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>6,25%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>4,39%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>27081</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>19846</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>35913</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17515</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31943</t>
+          <t>32166</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>17296</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32061</t>
+          <t>31653</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>37961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59724</t>
+          <t>59643</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>12331</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26773</t>
+          <t>25960</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15668</t>
+          <t>15671</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30615</t>
+          <t>30215</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30365</t>
+          <t>31325</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50546</t>
+          <t>52269</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16274</t>
+          <t>15594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30671</t>
+          <t>30369</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>18561</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34101</t>
+          <t>34699</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>37823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60083</t>
+          <t>59400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>118661</t>
+          <t>118808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140242</t>
+          <t>141133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>128749</t>
+          <t>128114</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>153154</t>
+          <t>151559</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>254547</t>
+          <t>254293</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>286042</t>
+          <t>287299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,28%</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15154</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8975</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>16052</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12176</t>
+          <t>12341</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17959</t>
+          <t>17855</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16036</t>
+          <t>15776</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8492</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20967</t>
+          <t>21019</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32184</t>
+          <t>31892</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45769</t>
+          <t>45739</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30699</t>
+          <t>30395</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41998</t>
+          <t>42041</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66511</t>
+          <t>65627</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>84224</t>
+          <t>84234</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,75%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31052</t>
+          <t>31270</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>17396</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33408</t>
+          <t>33433</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37266</t>
+          <t>38300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60892</t>
+          <t>59619</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41847</t>
+          <t>41511</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21758</t>
+          <t>23042</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39034</t>
+          <t>39199</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>50518</t>
+          <t>49646</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>74079</t>
+          <t>74728</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36410</t>
+          <t>35156</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24570</t>
+          <t>24539</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42103</t>
+          <t>42357</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46722</t>
+          <t>47465</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>71771</t>
+          <t>71949</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29423</t>
+          <t>29172</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t>47843</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27429</t>
+          <t>27728</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45909</t>
+          <t>44694</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60573</t>
+          <t>62134</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>87318</t>
+          <t>88881</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>188028</t>
+          <t>188446</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>216004</t>
+          <t>216084</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>195050</t>
+          <t>194452</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>222932</t>
+          <t>222776</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>388322</t>
+          <t>389522</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>429204</t>
+          <t>430425</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,9%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que se riesen de él/ella otros chicos en 2016 (tasa de respuesta: 98,52%)</t>
+          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el adulto en 2016 (tasa de respuesta: 98,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>553</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10756</t>
+          <t>10083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>876</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>8339</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9809</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>19819</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28002</t>
+          <t>27944</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21137</t>
+          <t>20570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30469</t>
+          <t>30185</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>44168</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56043</t>
+          <t>55941</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,72%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17680</t>
+          <t>17143</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19407</t>
+          <t>19355</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16091</t>
+          <t>16337</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32943</t>
+          <t>32859</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12727</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25988</t>
+          <t>26064</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12766</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>26611</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27892</t>
+          <t>28555</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48945</t>
+          <t>48416</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10440</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22350</t>
+          <t>24008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17244</t>
+          <t>18086</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33323</t>
+          <t>33179</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31087</t>
+          <t>30498</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51697</t>
+          <t>50483</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19258</t>
+          <t>19154</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35395</t>
+          <t>35792</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18703</t>
+          <t>18260</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34648</t>
+          <t>34067</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42347</t>
+          <t>42221</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64680</t>
+          <t>65936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166592</t>
+          <t>165877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>190332</t>
+          <t>189473</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149665</t>
+          <t>149413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175541</t>
+          <t>174453</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>321733</t>
+          <t>323374</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>357309</t>
+          <t>357868</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,48%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11081</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13575</t>
+          <t>13304</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4631</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>13928</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>10197</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>20371</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16176</t>
+          <t>16054</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19660</t>
+          <t>19385</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>16863</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31352</t>
+          <t>32018</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41383</t>
+          <t>40846</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54789</t>
+          <t>54130</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42581</t>
+          <t>42743</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57303</t>
+          <t>57028</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>88373</t>
+          <t>88057</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>107668</t>
+          <t>108379</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>71,09%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21052</t>
+          <t>20649</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14372</t>
+          <t>13792</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29025</t>
+          <t>29863</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25662</t>
+          <t>25172</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45668</t>
+          <t>44834</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18869</t>
+          <t>19291</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35410</t>
+          <t>35048</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17113</t>
+          <t>16873</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33560</t>
+          <t>33309</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40274</t>
+          <t>40707</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>63195</t>
+          <t>63790</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18057</t>
+          <t>18676</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34156</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24871</t>
+          <t>24689</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43593</t>
+          <t>42366</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46452</t>
+          <t>48256</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>70706</t>
+          <t>72384</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31016</t>
+          <t>30920</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50507</t>
+          <t>50458</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32343</t>
+          <t>32854</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53084</t>
+          <t>54111</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>68378</t>
+          <t>66607</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>95802</t>
+          <t>94505</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>236266</t>
+          <t>235151</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>264931</t>
+          <t>263536</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>222876</t>
+          <t>223033</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>253116</t>
+          <t>252592</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>468261</t>
+          <t>470256</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>509414</t>
+          <t>511187</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,53%</t>
         </is>
       </c>
     </row>
